--- a/RCS03N.xlsx
+++ b/RCS03N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="42">
   <si>
     <t/>
   </si>
@@ -74,12 +74,6 @@
   </si>
   <si>
     <t>SO GOOD JETS 400G</t>
-  </si>
-  <si>
-    <t>20051682</t>
-  </si>
-  <si>
-    <t>S/GOOD PAHA&amp;DADA 1KG</t>
   </si>
   <si>
     <t>20045443</t>
@@ -535,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -736,7 +730,7 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>4</v>
@@ -747,16 +741,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>4</v>
@@ -776,13 +770,13 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -796,13 +790,13 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -816,7 +810,7 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>4</v>
@@ -836,7 +830,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>4</v>
@@ -856,7 +850,7 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>4</v>
@@ -876,7 +870,7 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>4</v>
@@ -896,7 +890,7 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>4</v>
@@ -916,32 +910,12 @@
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="1" t="s">
         <v>5</v>
       </c>
     </row>
